--- a/sheets/민요/검수/한강수 타령.xlsx
+++ b/sheets/민요/검수/한강수 타령.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,42 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3936,8 +4052,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -3956,881 +4076,783 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">한강수 타령 — 민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">한강수 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">깊</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">한</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E4" s="16"/>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G4" s="16"/>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I4" s="16"/>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K4" s="16"/>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M4" s="16"/>
+      <c r="N4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O4" s="16"/>
+      <c r="P4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q4" s="16"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C5" s="17"/>
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="E5" s="17"/>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G5" s="17"/>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I5" s="17"/>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K5" s="17"/>
+      <c r="L5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q5" s="2"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="M5" s="17"/>
+      <c r="N5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O5" s="17"/>
+      <c r="P5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q5" s="17"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">싸</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="Q6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="E7" s="16"/>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G7" s="16"/>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I7" s="16"/>
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="K7" s="16"/>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M7" s="16"/>
+      <c r="N7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="O7" s="16"/>
+      <c r="P7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q7" s="16"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C8" s="17"/>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E8" s="17"/>
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="G8" s="17"/>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I8" s="17"/>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K8" s="17"/>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M8" s="17"/>
+      <c r="N8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="O8" s="5"/>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q8" s="2"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="O8" s="18"/>
+      <c r="P8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q8" s="17"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">양</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">백</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">맑</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="16"/>
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="16"/>
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="G10" s="16"/>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I10" s="16"/>
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="K10" s="16"/>
+      <c r="L10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="M10" s="16"/>
+      <c r="N10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="O10" s="16"/>
+      <c r="P10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="Q10" s="16"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C11" s="17"/>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E11" s="17"/>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G11" s="17"/>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I11" s="17"/>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K11" s="17"/>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M11" s="17"/>
+      <c r="N11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="O11" s="17"/>
+      <c r="P11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="Q11" s="17"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C13" s="16"/>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E13" s="16"/>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G13" s="16"/>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I13" s="16"/>
+      <c r="J13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K13" s="16"/>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M13" s="16"/>
+      <c r="N13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O13" s="16"/>
+      <c r="P13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q13" s="16"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q14" s="2"/>
+          </r>
+        </is>
+      </c>
+      <c r="C14" s="17"/>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E14" s="17"/>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G14" s="17"/>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I14" s="17"/>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K14" s="17"/>
+      <c r="L14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M14" s="17"/>
+      <c r="N14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O14" s="17"/>
+      <c r="P14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q14" s="17"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:Q2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/한강수 타령.xlsx
+++ b/sheets/민요/검수/한강수 타령.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -697,12 +697,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|·</t>
+          <t xml:space="preserve">–|·</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -926,12 +926,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I12" s="2"/>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|·</t>
+          <t xml:space="preserve">–|·</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|·</t>
+          <t xml:space="preserve">–|·</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|·</t>
+          <t xml:space="preserve">–|·</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -1847,12 +1847,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -2428,12 +2428,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|·</t>
+          <t xml:space="preserve">–|·</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I57" s="2"/>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|·</t>
+          <t xml:space="preserve">–|·</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -3044,12 +3044,12 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|·</t>
+          <t xml:space="preserve">–|·</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I75" s="2"/>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|·</t>
+          <t xml:space="preserve">–|·</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -4040,12 +4040,12 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|·</t>
+          <t xml:space="preserve">–|·</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -4318,7 +4318,7 @@
       <c r="C4" s="9"/>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E4" s="9"/>
@@ -4331,7 +4331,7 @@
       <c r="G4" s="9"/>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="L4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="N5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="L6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -4541,7 +4541,7 @@
       <c r="E7" s="9"/>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -4587,7 +4587,7 @@
       <c r="O7" s="9"/>
       <c r="P7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="L8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -4788,7 +4788,7 @@
       <c r="G10" s="9"/>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="9"/>
@@ -4835,7 +4835,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="N11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="L13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M13" s="9" t="inlineStr">
@@ -5076,7 +5076,7 @@
       <c r="O13" s="9"/>
       <c r="P13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q13" s="9"/>
@@ -5085,14 +5085,14 @@
       <c r="A14" s="0"/>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -5123,7 +5123,7 @@
       <c r="M14" s="10"/>
       <c r="N14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O14" s="10"/>

--- a/sheets/민요/검수/한강수 타령.xlsx
+++ b/sheets/민요/검수/한강수 타령.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4204,105 +4239,105 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">한강수 타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">한</t>
         </is>
@@ -4310,220 +4345,220 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="23"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="23"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="G4" s="23"/>
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="O4" s="23"/>
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q4" s="9"/>
+      <c r="Q4" s="23"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="24"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에에</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="K5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr">
+      <c r="M5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="O5" s="10" t="inlineStr">
+      <c r="O5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q5" s="10"/>
+      <c r="Q5" s="24"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 ·</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="G6" s="22"/>
+      <c r="H6" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J6" s="18" t="inlineStr">
+      <c r="J6" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">뱃</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">뱃</t>
         </is>
       </c>
-      <c r="N6" s="18" t="inlineStr">
+      <c r="N6" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="O6" s="11"/>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="O6" s="26"/>
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
@@ -4531,227 +4566,227 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="B7" s="21"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="23"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="I7" s="23"/>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="O7" s="9"/>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="O7" s="23"/>
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
-      <c r="Q7" s="9"/>
+      <c r="Q7" s="23"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="24"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K8" s="10" t="inlineStr">
+      <c r="K8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O8" s="10" t="inlineStr">
+      <c r="O8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">선</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q8" s="10"/>
+      <c r="Q8" s="24"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">등</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
@@ -4759,73 +4794,73 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="23"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="23"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="K10" s="23"/>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O10" s="9" t="inlineStr">
+      <c r="O10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="Q10" s="9" t="inlineStr">
+      <c r="Q10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
@@ -4833,90 +4868,90 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">앙</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">앙</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 姑</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에에</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="K11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">안</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="O11" s="10" t="inlineStr">
+      <c r="O11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="Q11" s="10" t="inlineStr">
+      <c r="Q11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
@@ -4924,83 +4959,83 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아아</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아아</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -5008,131 +5043,131 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O13" s="9"/>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="O13" s="23"/>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q13" s="9"/>
+      <c r="Q13" s="23"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="24"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="24"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="24"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="24"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="24"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="M14" s="24"/>
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="O14" s="24"/>
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q14" s="10"/>
+      <c r="Q14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/한강수 타령.xlsx
+++ b/sheets/민요/검수/한강수 타령.xlsx
@@ -4216,28 +4216,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4343,11 +4343,11 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C4" s="23"/>
@@ -4367,7 +4367,7 @@
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-·</t>
+–</t>
         </is>
       </c>
       <c r="I4" s="23" t="inlineStr">
@@ -4388,7 +4388,7 @@
       <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-·</t>
+–</t>
         </is>
       </c>
       <c r="M4" s="23" t="inlineStr">
@@ -4404,16 +4404,16 @@
       <c r="O4" s="23"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C5" s="24"/>
@@ -4482,17 +4482,17 @@
       </c>
       <c r="P5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-·</t>
+–</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E6" s="26" t="inlineStr">
@@ -4539,7 +4539,7 @@
       <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-·</t>
+–</t>
         </is>
       </c>
       <c r="M6" s="22" t="inlineStr">
@@ -4564,7 +4564,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -4577,7 +4577,7 @@
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-·</t>
+–</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
@@ -4623,12 +4623,12 @@
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-·</t>
+–</t>
         </is>
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-·</t>
+–</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -4654,7 +4654,7 @@
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-·</t>
+–</t>
         </is>
       </c>
       <c r="G8" s="24"/>
@@ -4683,7 +4683,7 @@
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-·</t>
+–</t>
         </is>
       </c>
       <c r="M8" s="24" t="inlineStr">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="P8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5116,12 +5116,12 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-·</t>
+–</t>
         </is>
       </c>
       <c r="C14" s="24"/>
@@ -5134,25 +5134,25 @@
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I14" s="24"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K14" s="24"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M14" s="24"/>
@@ -5164,7 +5164,7 @@
       <c r="O14" s="24"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q14" s="24"/>

--- a/sheets/민요/검수/한강수 타령.xlsx
+++ b/sheets/민요/검수/한강수 타령.xlsx
@@ -4445,7 +4445,8 @@
       </c>
       <c r="I5" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">에에</t>
+          <t xml:space="preserve">에
+에</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -4909,7 +4910,8 @@
       </c>
       <c r="I11" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">에에</t>
+          <t xml:space="preserve">에
+에</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -4967,7 +4969,8 @@
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">아아</t>
+          <t xml:space="preserve">아
+아</t>
         </is>
       </c>
       <c r="D12" s="25" t="inlineStr">
@@ -4977,7 +4980,8 @@
       </c>
       <c r="E12" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">아아</t>
+          <t xml:space="preserve">아
+아</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">

--- a/sheets/민요/검수/한강수 타령.xlsx
+++ b/sheets/민요/검수/한강수 타령.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -230,6 +235,18 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4267,7 +4284,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
@@ -4277,7 +4294,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
@@ -4287,7 +4304,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
@@ -4297,7 +4314,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4307,7 +4324,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4317,7 +4334,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4327,7 +4344,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
@@ -4337,7 +4354,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q3" s="22" t="inlineStr">
+      <c r="Q3" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">한</t>
         </is>
@@ -4350,27 +4367,27 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C4" s="23"/>
+      <c r="C4" s="28"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="28"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G4" s="23"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="I4" s="23" t="inlineStr">
+      <c r="I4" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
@@ -4380,7 +4397,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K4" s="23" t="inlineStr">
+      <c r="K4" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
@@ -4391,7 +4408,7 @@
 –</t>
         </is>
       </c>
-      <c r="M4" s="23" t="inlineStr">
+      <c r="M4" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
@@ -4401,13 +4418,13 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O4" s="23"/>
+      <c r="O4" s="28"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q4" s="23"/>
+      <c r="Q4" s="28"/>
     </row>
     <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
@@ -4416,13 +4433,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="24"/>
+      <c r="C5" s="29"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
@@ -4433,7 +4450,7 @@
 南</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
@@ -4443,7 +4460,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I5" s="24" t="inlineStr">
+      <c r="I5" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에
 에</t>
@@ -4455,7 +4472,7 @@
 無</t>
         </is>
       </c>
-      <c r="K5" s="24" t="inlineStr">
+      <c r="K5" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -4465,7 +4482,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M5" s="24" t="inlineStr">
+      <c r="M5" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -4476,7 +4493,7 @@
 無</t>
         </is>
       </c>
-      <c r="O5" s="24" t="inlineStr">
+      <c r="O5" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
@@ -4486,7 +4503,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q5" s="24"/>
+      <c r="Q5" s="29"/>
     </row>
     <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
@@ -4496,7 +4513,7 @@
 –</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -4506,7 +4523,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -4516,13 +4533,13 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G6" s="22"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I6" s="26" t="inlineStr">
+      <c r="I6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4532,7 +4549,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="K6" s="26" t="inlineStr">
+      <c r="K6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">뱃</t>
         </is>
@@ -4543,7 +4560,7 @@
 –</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="M6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">뱃</t>
         </is>
@@ -4553,13 +4570,13 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="O6" s="26"/>
+      <c r="O6" s="30"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="Q6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
@@ -4568,20 +4585,20 @@
     <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
-      <c r="C7" s="23"/>
+      <c r="C7" s="28"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="28"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="G7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
@@ -4592,14 +4609,14 @@
 㳞</t>
         </is>
       </c>
-      <c r="I7" s="23"/>
+      <c r="I7" s="28"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="K7" s="23" t="inlineStr">
+      <c r="K7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
@@ -4609,7 +4626,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M7" s="23" t="inlineStr">
+      <c r="M7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
@@ -4620,14 +4637,14 @@
 㳞</t>
         </is>
       </c>
-      <c r="O7" s="23"/>
+      <c r="O7" s="28"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="Q7" s="23"/>
+      <c r="Q7" s="28"/>
     </row>
     <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
@@ -4636,7 +4653,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4647,7 +4664,7 @@
 –</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
@@ -4658,14 +4675,14 @@
 –</t>
         </is>
       </c>
-      <c r="G8" s="24"/>
+      <c r="G8" s="29"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I8" s="24" t="inlineStr">
+      <c r="I8" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -4676,7 +4693,7 @@
 無</t>
         </is>
       </c>
-      <c r="K8" s="24" t="inlineStr">
+      <c r="K8" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4687,7 +4704,7 @@
 –</t>
         </is>
       </c>
-      <c r="M8" s="24" t="inlineStr">
+      <c r="M8" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4698,7 +4715,7 @@
 無</t>
         </is>
       </c>
-      <c r="O8" s="24" t="inlineStr">
+      <c r="O8" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">선</t>
         </is>
@@ -4708,7 +4725,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q8" s="24"/>
+      <c r="Q8" s="29"/>
     </row>
     <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
@@ -4717,7 +4734,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
@@ -4727,7 +4744,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
@@ -4737,7 +4754,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">등</t>
         </is>
@@ -4747,7 +4764,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4757,7 +4774,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4767,7 +4784,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M9" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -4777,7 +4794,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="O9" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -4787,7 +4804,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q9" s="22" t="inlineStr">
+      <c r="Q9" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
@@ -4800,7 +4817,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4810,7 +4827,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4821,26 +4838,26 @@
 潢</t>
         </is>
       </c>
-      <c r="G10" s="23"/>
+      <c r="G10" s="28"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I10" s="23"/>
+      <c r="I10" s="28"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K10" s="23"/>
+      <c r="K10" s="28"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="M10" s="23" t="inlineStr">
+      <c r="M10" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
@@ -4850,7 +4867,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O10" s="23" t="inlineStr">
+      <c r="O10" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -4861,7 +4878,7 @@
 潢</t>
         </is>
       </c>
-      <c r="Q10" s="23" t="inlineStr">
+      <c r="Q10" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
@@ -4875,7 +4892,7 @@
 南</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">앙</t>
         </is>
@@ -4885,7 +4902,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">앙</t>
         </is>
@@ -4896,7 +4913,7 @@
 南</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="G11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
@@ -4908,7 +4925,7 @@
 姑</t>
         </is>
       </c>
-      <c r="I11" s="24" t="inlineStr">
+      <c r="I11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에
 에</t>
@@ -4920,7 +4937,7 @@
 南</t>
         </is>
       </c>
-      <c r="K11" s="24" t="inlineStr">
+      <c r="K11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4931,7 +4948,7 @@
 南</t>
         </is>
       </c>
-      <c r="M11" s="24" t="inlineStr">
+      <c r="M11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">안</t>
         </is>
@@ -4942,7 +4959,7 @@
 南</t>
         </is>
       </c>
-      <c r="O11" s="24" t="inlineStr">
+      <c r="O11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
@@ -4953,7 +4970,7 @@
 南</t>
         </is>
       </c>
-      <c r="Q11" s="24" t="inlineStr">
+      <c r="Q11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
@@ -4967,7 +4984,7 @@
 南</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 아</t>
@@ -4978,7 +4995,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 아</t>
@@ -4989,7 +5006,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
@@ -4999,7 +5016,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -5009,7 +5026,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
@@ -5019,7 +5036,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5029,7 +5046,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O12" s="22" t="inlineStr">
+      <c r="O12" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -5039,7 +5056,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q12" s="22" t="inlineStr">
+      <c r="Q12" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -5052,7 +5069,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5062,7 +5079,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5072,7 +5089,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr">
+      <c r="G13" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5082,7 +5099,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I13" s="23" t="inlineStr">
+      <c r="I13" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5092,7 +5109,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K13" s="23" t="inlineStr">
+      <c r="K13" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
@@ -5102,7 +5119,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M13" s="23" t="inlineStr">
+      <c r="M13" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5112,13 +5129,13 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O13" s="23"/>
+      <c r="O13" s="28"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q13" s="23"/>
+      <c r="Q13" s="28"/>
     </row>
     <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
@@ -5128,50 +5145,50 @@
 –</t>
         </is>
       </c>
-      <c r="C14" s="24"/>
+      <c r="C14" s="29"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="E14" s="24"/>
+      <c r="E14" s="29"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="24"/>
+      <c r="G14" s="29"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I14" s="24"/>
+      <c r="I14" s="29"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="24"/>
+      <c r="K14" s="29"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M14" s="24"/>
+      <c r="M14" s="29"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O14" s="24"/>
+      <c r="O14" s="29"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q14" s="24"/>
+      <c r="Q14" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/한강수 타령.xlsx
+++ b/sheets/민요/검수/한강수 타령.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -223,28 +218,22 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -341,7 +330,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">95</t>
+          <t xml:space="preserve">87</t>
         </is>
       </c>
     </row>
@@ -353,7 +342,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
     </row>
@@ -413,7 +402,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">오른쪽 여백에 세로로 "한강수 타령 굿거리" 표기. 12정간 양식, 굵은 선 3칸마다. 8줄 모두 사용. 손글씨가 빽빽하고 겹쳐 쓴 곳이 많아 일부 율명·가사 불확실. 하단 "- 197 -"은 양식 용지 번호. AI 재판독 초안.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식 12정간(굵은 선 3칸마다, 줄 번호 1~8), 8줄 모두 사용. 오른쪽 여백에 세로로 "한강수 타령 굿거리" 표기. 줄5~8은 후렴(에헤 에헤요 얼삼마 둥개디어라 내사랑아). 가사는 각 율명 줄 오른쪽 칸. 하단 "- 197 -"은 양식 용지 번호.</t>
         </is>
       </c>
     </row>
@@ -747,19 +736,22 @@
       <c r="F6" s="2">
         <v>2</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|·</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-·</t>
-        </is>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="4"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">– 아래 작은 꼬리</t>
+        </is>
+      </c>
       <c r="K6" s="2"/>
     </row>
     <row r="7">
@@ -1013,12 +1005,13 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I13" s="2"/>
@@ -1058,7 +1051,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">수</t>
+          <t xml:space="preserve">깊</t>
         </is>
       </c>
       <c r="J14" s="4"/>
@@ -1095,7 +1088,11 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I15" s="2"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
       <c r="J15" s="4"/>
       <c r="K15" s="2"/>
     </row>
@@ -1133,7 +1130,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삼</t>
+          <t xml:space="preserve">오</t>
         </is>
       </c>
       <c r="J16" s="4"/>
@@ -1160,22 +1157,22 @@
       <c r="F17" s="2">
         <v>2</v>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I17" s="3"/>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞(氵仲)</t>
-        </is>
-      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">깊</t>
+        </is>
+      </c>
+      <c r="J17" s="4"/>
       <c r="K17" s="2"/>
     </row>
     <row r="18">
@@ -1201,16 +1198,20 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|㳞</t>
+          <t xml:space="preserve">潢|㴌</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-㳞</t>
-        </is>
-      </c>
-      <c r="I18" s="2"/>
+㴌</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">은</t>
+        </is>
+      </c>
       <c r="J18" s="4"/>
       <c r="K18" s="2"/>
     </row>
@@ -1235,23 +1236,27 @@
       <c r="F19" s="2">
         <v>2</v>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢|無</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">선</t>
-        </is>
-      </c>
-      <c r="J19" s="4"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">으은</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아래 경계에 &lt; 표시</t>
+        </is>
+      </c>
       <c r="K19" s="2"/>
     </row>
     <row r="20">
@@ -1287,7 +1292,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">라</t>
+          <t xml:space="preserve">물</t>
         </is>
       </c>
       <c r="J20" s="4"/>
@@ -1326,7 +1331,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">고</t>
+          <t xml:space="preserve">울</t>
         </is>
       </c>
       <c r="J21" s="4"/>
@@ -1366,7 +1371,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">오</t>
+          <t xml:space="preserve">에</t>
         </is>
       </c>
       <c r="J22" s="4"/>
@@ -1405,7 +1410,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서</t>
+          <t xml:space="preserve">에</t>
         </is>
       </c>
       <c r="J23" s="4"/>
@@ -1442,7 +1447,11 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I24" s="2"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤</t>
+        </is>
+      </c>
       <c r="J24" s="4"/>
       <c r="K24" s="2"/>
     </row>
@@ -1469,12 +1478,13 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -1514,7 +1524,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에</t>
+          <t xml:space="preserve">수</t>
         </is>
       </c>
       <c r="J26" s="4"/>
@@ -1536,25 +1546,24 @@
         <v>3</v>
       </c>
       <c r="E27" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="2">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|·</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-·</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">루</t>
+          <t xml:space="preserve">상</t>
         </is>
       </c>
       <c r="J27" s="4"/>
@@ -1576,10 +1585,10 @@
         <v>3</v>
       </c>
       <c r="E28" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F28" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -1593,7 +1602,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">화</t>
+          <t xml:space="preserve">선</t>
         </is>
       </c>
       <c r="J28" s="4"/>
@@ -1615,28 +1624,31 @@
         <v>3</v>
       </c>
       <c r="E29" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F29" s="2">
-        <v>2</v>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|·</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-·</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">뱃</t>
-        </is>
-      </c>
-      <c r="J29" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 타/라?</t>
+        </is>
+      </c>
       <c r="K29" s="2"/>
     </row>
     <row r="30">
@@ -1655,24 +1667,25 @@
         <v>3</v>
       </c>
       <c r="E30" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F30" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">無|潢</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">無
+潢</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">놀</t>
+          <t xml:space="preserve">고</t>
         </is>
       </c>
       <c r="J30" s="4"/>
@@ -1694,25 +1707,25 @@
         <v>3</v>
       </c>
       <c r="E31" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F31" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|·</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-·</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이</t>
+          <t xml:space="preserve">오</t>
         </is>
       </c>
       <c r="J31" s="4"/>
@@ -1734,24 +1747,24 @@
         <v>3</v>
       </c>
       <c r="E32" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F32" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가</t>
+          <t xml:space="preserve">서</t>
         </is>
       </c>
       <c r="J32" s="4"/>
@@ -1773,995 +1786,995 @@
         <v>3</v>
       </c>
       <c r="E33" s="2">
+        <v>11</v>
+      </c>
+      <c r="F33" s="2">
+        <v>4</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I33" s="2"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2">
+        <v>1</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C34" s="2">
+        <v>3</v>
+      </c>
+      <c r="D34" s="2">
+        <v>3</v>
+      </c>
+      <c r="E34" s="2">
+        <v>12</v>
+      </c>
+      <c r="F34" s="2">
+        <v>4</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I34" s="2"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2">
+        <v>1</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C35" s="2">
+        <v>4</v>
+      </c>
+      <c r="D35" s="2">
+        <v>4</v>
+      </c>
+      <c r="E35" s="2">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="J35" s="4"/>
+      <c r="K35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2">
+        <v>1</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C36" s="2">
+        <v>4</v>
+      </c>
+      <c r="D36" s="2">
+        <v>4</v>
+      </c>
+      <c r="E36" s="2">
+        <v>2</v>
+      </c>
+      <c r="F36" s="2">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">루</t>
+        </is>
+      </c>
+      <c r="J36" s="4"/>
+      <c r="K36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2">
+        <v>1</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C37" s="2">
+        <v>4</v>
+      </c>
+      <c r="D37" s="2">
+        <v>4</v>
+      </c>
+      <c r="E37" s="2">
+        <v>3</v>
+      </c>
+      <c r="F37" s="2">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|無</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+無</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화</t>
+        </is>
+      </c>
+      <c r="J37" s="4"/>
+      <c r="K37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2">
+        <v>1</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C38" s="2">
+        <v>4</v>
+      </c>
+      <c r="D38" s="2">
+        <v>4</v>
+      </c>
+      <c r="E38" s="2">
+        <v>4</v>
+      </c>
+      <c r="F38" s="2">
+        <v>2</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">뱃</t>
+        </is>
+      </c>
+      <c r="J38" s="4"/>
+      <c r="K38" s="2"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2">
+        <v>1</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C39" s="2">
+        <v>4</v>
+      </c>
+      <c r="D39" s="2">
+        <v>4</v>
+      </c>
+      <c r="E39" s="2">
+        <v>5</v>
+      </c>
+      <c r="F39" s="2">
+        <v>2</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|㴌</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">놀</t>
+        </is>
+      </c>
+      <c r="J39" s="4"/>
+      <c r="K39" s="2"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2">
+        <v>1</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C40" s="2">
+        <v>4</v>
+      </c>
+      <c r="D40" s="2">
+        <v>4</v>
+      </c>
+      <c r="E40" s="2">
+        <v>6</v>
+      </c>
+      <c r="F40" s="2">
+        <v>2</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|無</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="J40" s="4"/>
+      <c r="K40" s="2"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2">
+        <v>1</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C41" s="2">
+        <v>4</v>
+      </c>
+      <c r="D41" s="2">
+        <v>4</v>
+      </c>
+      <c r="E41" s="2">
+        <v>7</v>
+      </c>
+      <c r="F41" s="2">
+        <v>3</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
+      <c r="J41" s="4"/>
+      <c r="K41" s="2"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2">
+        <v>1</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C42" s="2">
+        <v>4</v>
+      </c>
+      <c r="D42" s="2">
+        <v>4</v>
+      </c>
+      <c r="E42" s="2">
         <v>8</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F42" s="2">
         <v>3</v>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잔</t>
+        </is>
+      </c>
+      <c r="J42" s="4"/>
+      <c r="K42" s="2"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <v>1</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C43" s="2">
+        <v>4</v>
+      </c>
+      <c r="D43" s="2">
+        <v>4</v>
+      </c>
+      <c r="E43" s="2">
+        <v>9</v>
+      </c>
+      <c r="F43" s="2">
+        <v>3</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|南</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">안</t>
+        </is>
+      </c>
+      <c r="J43" s="4"/>
+      <c r="K43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <v>1</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C44" s="2">
+        <v>4</v>
+      </c>
+      <c r="D44" s="2">
+        <v>4</v>
+      </c>
+      <c r="E44" s="2">
+        <v>10</v>
+      </c>
+      <c r="F44" s="2">
+        <v>4</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="J44" s="4"/>
+      <c r="K44" s="2"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <v>1</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C45" s="2">
+        <v>4</v>
+      </c>
+      <c r="D45" s="2">
+        <v>4</v>
+      </c>
+      <c r="E45" s="2">
+        <v>11</v>
+      </c>
+      <c r="F45" s="2">
+        <v>4</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="J45" s="4"/>
+      <c r="K45" s="2"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <v>1</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C46" s="2">
+        <v>4</v>
+      </c>
+      <c r="D46" s="2">
+        <v>4</v>
+      </c>
+      <c r="E46" s="2">
+        <v>12</v>
+      </c>
+      <c r="F46" s="2">
+        <v>4</v>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I46" s="3"/>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△ 작고 흐림</t>
+        </is>
+      </c>
+      <c r="K46" s="2"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <v>1</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C47" s="2">
+        <v>5</v>
+      </c>
+      <c r="D47" s="2">
+        <v>5</v>
+      </c>
+      <c r="E47" s="2">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="J47" s="4"/>
+      <c r="K47" s="2"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <v>1</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C48" s="2">
+        <v>5</v>
+      </c>
+      <c r="D48" s="2">
+        <v>5</v>
+      </c>
+      <c r="E48" s="2">
+        <v>3</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하</t>
+        </is>
+      </c>
+      <c r="J48" s="4"/>
+      <c r="K48" s="2"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2">
+        <v>1</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C49" s="2">
+        <v>5</v>
+      </c>
+      <c r="D49" s="2">
+        <v>5</v>
+      </c>
+      <c r="E49" s="2">
+        <v>4</v>
+      </c>
+      <c r="F49" s="2">
+        <v>2</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="J49" s="4"/>
+      <c r="K49" s="2"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <v>1</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C50" s="2">
+        <v>5</v>
+      </c>
+      <c r="D50" s="2">
+        <v>5</v>
+      </c>
+      <c r="E50" s="2">
+        <v>6</v>
+      </c>
+      <c r="F50" s="2">
+        <v>2</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하</t>
+        </is>
+      </c>
+      <c r="J50" s="4"/>
+      <c r="K50" s="2"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <v>1</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C51" s="2">
+        <v>5</v>
+      </c>
+      <c r="D51" s="2">
+        <v>5</v>
+      </c>
+      <c r="E51" s="2">
+        <v>7</v>
+      </c>
+      <c r="F51" s="2">
+        <v>3</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="J51" s="4"/>
+      <c r="K51" s="2"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2">
+        <v>1</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C52" s="2">
+        <v>5</v>
+      </c>
+      <c r="D52" s="2">
+        <v>5</v>
+      </c>
+      <c r="E52" s="2">
+        <v>9</v>
+      </c>
+      <c r="F52" s="2">
+        <v>3</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|無|南</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤</t>
+        </is>
+      </c>
+      <c r="J52" s="4"/>
+      <c r="K52" s="2"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2">
+        <v>1</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C53" s="2">
+        <v>5</v>
+      </c>
+      <c r="D53" s="2">
+        <v>5</v>
+      </c>
+      <c r="E53" s="2">
+        <v>10</v>
+      </c>
+      <c r="F53" s="2">
+        <v>4</v>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요</t>
+        </is>
+      </c>
+      <c r="J53" s="4"/>
+      <c r="K53" s="2"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2">
+        <v>1</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C54" s="2">
+        <v>5</v>
+      </c>
+      <c r="D54" s="2">
+        <v>5</v>
+      </c>
+      <c r="E54" s="2">
+        <v>11</v>
+      </c>
+      <c r="F54" s="2">
+        <v>4</v>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오</t>
+        </is>
+      </c>
+      <c r="J54" s="4"/>
+      <c r="K54" s="2"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2">
+        <v>1</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C55" s="2">
+        <v>5</v>
+      </c>
+      <c r="D55" s="2">
+        <v>5</v>
+      </c>
+      <c r="E55" s="2">
+        <v>12</v>
+      </c>
+      <c r="F55" s="2">
+        <v>4</v>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I55" s="2"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="2"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2">
+        <v>1</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C56" s="2">
+        <v>6</v>
+      </c>
+      <c r="D56" s="2">
+        <v>6</v>
+      </c>
+      <c r="E56" s="2">
+        <v>1</v>
+      </c>
+      <c r="F56" s="2">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="J56" s="4"/>
+      <c r="K56" s="2"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2">
+        <v>1</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C57" s="2">
+        <v>6</v>
+      </c>
+      <c r="D57" s="2">
+        <v>6</v>
+      </c>
+      <c r="E57" s="2">
+        <v>2</v>
+      </c>
+      <c r="F57" s="2">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無|潢</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전</t>
-        </is>
-      </c>
-      <c r="J33" s="4"/>
-      <c r="K33" s="2"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2">
-        <v>1</v>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C34" s="2">
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤</t>
+        </is>
+      </c>
+      <c r="J57" s="4"/>
+      <c r="K57" s="2"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2">
+        <v>1</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
+        </is>
+      </c>
+      <c r="C58" s="2">
+        <v>6</v>
+      </c>
+      <c r="D58" s="2">
+        <v>6</v>
+      </c>
+      <c r="E58" s="2">
         <v>3</v>
       </c>
-      <c r="D34" s="2">
-        <v>3</v>
-      </c>
-      <c r="E34" s="2">
-        <v>9</v>
-      </c>
-      <c r="F34" s="2">
-        <v>3</v>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="F58" s="2">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無|南</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">안</t>
-        </is>
-      </c>
-      <c r="J34" s="4"/>
-      <c r="K34" s="2"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2">
-        <v>1</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C35" s="2">
-        <v>3</v>
-      </c>
-      <c r="D35" s="2">
-        <v>3</v>
-      </c>
-      <c r="E35" s="2">
-        <v>10</v>
-      </c>
-      <c r="F35" s="2">
-        <v>4</v>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
-      <c r="J35" s="4"/>
-      <c r="K35" s="2"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2">
-        <v>1</v>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C36" s="2">
-        <v>3</v>
-      </c>
-      <c r="D36" s="2">
-        <v>3</v>
-      </c>
-      <c r="E36" s="2">
-        <v>11</v>
-      </c>
-      <c r="F36" s="2">
-        <v>4</v>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="J36" s="4"/>
-      <c r="K36" s="2"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2">
-        <v>1</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C37" s="2">
-        <v>3</v>
-      </c>
-      <c r="D37" s="2">
-        <v>3</v>
-      </c>
-      <c r="E37" s="2">
-        <v>12</v>
-      </c>
-      <c r="F37" s="2">
-        <v>4</v>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I37" s="2"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="2"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2">
-        <v>1</v>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C38" s="2">
-        <v>4</v>
-      </c>
-      <c r="D38" s="2">
-        <v>4</v>
-      </c>
-      <c r="E38" s="2">
-        <v>1</v>
-      </c>
-      <c r="F38" s="2">
-        <v>1</v>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="J38" s="4"/>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2">
-        <v>1</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C39" s="2">
-        <v>4</v>
-      </c>
-      <c r="D39" s="2">
-        <v>4</v>
-      </c>
-      <c r="E39" s="2">
-        <v>2</v>
-      </c>
-      <c r="F39" s="2">
-        <v>1</v>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">루</t>
-        </is>
-      </c>
-      <c r="J39" s="4"/>
-      <c r="K39" s="2"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2">
-        <v>1</v>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C40" s="2">
-        <v>4</v>
-      </c>
-      <c r="D40" s="2">
-        <v>4</v>
-      </c>
-      <c r="E40" s="2">
-        <v>3</v>
-      </c>
-      <c r="F40" s="2">
-        <v>1</v>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|無</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-無</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">화</t>
-        </is>
-      </c>
-      <c r="J40" s="4"/>
-      <c r="K40" s="2"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2">
-        <v>1</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C41" s="2">
-        <v>4</v>
-      </c>
-      <c r="D41" s="2">
-        <v>4</v>
-      </c>
-      <c r="E41" s="2">
-        <v>4</v>
-      </c>
-      <c r="F41" s="2">
-        <v>2</v>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">뱃</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞(氵仲)</t>
-        </is>
-      </c>
-      <c r="K41" s="2"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2">
-        <v>1</v>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C42" s="2">
-        <v>4</v>
-      </c>
-      <c r="D42" s="2">
-        <v>4</v>
-      </c>
-      <c r="E42" s="2">
-        <v>5</v>
-      </c>
-      <c r="F42" s="2">
-        <v>2</v>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|㳞</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-㳞</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">놀</t>
-        </is>
-      </c>
-      <c r="J42" s="4"/>
-      <c r="K42" s="2"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2">
-        <v>1</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C43" s="2">
-        <v>4</v>
-      </c>
-      <c r="D43" s="2">
-        <v>4</v>
-      </c>
-      <c r="E43" s="2">
-        <v>6</v>
-      </c>
-      <c r="F43" s="2">
-        <v>2</v>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|無</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="J43" s="4"/>
-      <c r="K43" s="2"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2">
-        <v>1</v>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C44" s="2">
-        <v>4</v>
-      </c>
-      <c r="D44" s="2">
-        <v>4</v>
-      </c>
-      <c r="E44" s="2">
-        <v>7</v>
-      </c>
-      <c r="F44" s="2">
-        <v>3</v>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="J44" s="4"/>
-      <c r="K44" s="2"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2">
-        <v>1</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C45" s="2">
-        <v>4</v>
-      </c>
-      <c r="D45" s="2">
-        <v>4</v>
-      </c>
-      <c r="E45" s="2">
-        <v>8</v>
-      </c>
-      <c r="F45" s="2">
-        <v>3</v>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I45" s="2"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="2"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2">
-        <v>1</v>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C46" s="2">
-        <v>4</v>
-      </c>
-      <c r="D46" s="2">
-        <v>4</v>
-      </c>
-      <c r="E46" s="2">
-        <v>9</v>
-      </c>
-      <c r="F46" s="2">
-        <v>3</v>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|南</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-南</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="J46" s="4"/>
-      <c r="K46" s="2"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2">
-        <v>1</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C47" s="2">
-        <v>4</v>
-      </c>
-      <c r="D47" s="2">
-        <v>4</v>
-      </c>
-      <c r="E47" s="2">
-        <v>10</v>
-      </c>
-      <c r="F47" s="2">
-        <v>4</v>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요</t>
-        </is>
-      </c>
-      <c r="J47" s="4"/>
-      <c r="K47" s="2"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2">
-        <v>1</v>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C48" s="2">
-        <v>4</v>
-      </c>
-      <c r="D48" s="2">
-        <v>4</v>
-      </c>
-      <c r="E48" s="2">
-        <v>11</v>
-      </c>
-      <c r="F48" s="2">
-        <v>4</v>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">오</t>
-        </is>
-      </c>
-      <c r="J48" s="4"/>
-      <c r="K48" s="2"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2">
-        <v>1</v>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C49" s="2">
-        <v>4</v>
-      </c>
-      <c r="D49" s="2">
-        <v>4</v>
-      </c>
-      <c r="E49" s="2">
-        <v>12</v>
-      </c>
-      <c r="F49" s="2">
-        <v>4</v>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I49" s="2"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="2"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2">
-        <v>1</v>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C50" s="2">
-        <v>5</v>
-      </c>
-      <c r="D50" s="2">
-        <v>5</v>
-      </c>
-      <c r="E50" s="2">
-        <v>1</v>
-      </c>
-      <c r="F50" s="2">
-        <v>1</v>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="J50" s="4"/>
-      <c r="K50" s="2"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2">
-        <v>1</v>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C51" s="2">
-        <v>5</v>
-      </c>
-      <c r="D51" s="2">
-        <v>5</v>
-      </c>
-      <c r="E51" s="2">
-        <v>2</v>
-      </c>
-      <c r="F51" s="2">
-        <v>1</v>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|·</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-·</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">헤</t>
-        </is>
-      </c>
-      <c r="J51" s="4"/>
-      <c r="K51" s="2"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2">
-        <v>1</v>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C52" s="2">
-        <v>5</v>
-      </c>
-      <c r="D52" s="2">
-        <v>5</v>
-      </c>
-      <c r="E52" s="2">
-        <v>3</v>
-      </c>
-      <c r="F52" s="2">
-        <v>1</v>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에에</t>
-        </is>
-      </c>
-      <c r="J52" s="4"/>
-      <c r="K52" s="2"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2">
-        <v>1</v>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C53" s="2">
-        <v>5</v>
-      </c>
-      <c r="D53" s="2">
-        <v>5</v>
-      </c>
-      <c r="E53" s="2">
-        <v>4</v>
-      </c>
-      <c r="F53" s="2">
-        <v>2</v>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞(氵仲)</t>
-        </is>
-      </c>
-      <c r="K53" s="2"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2">
-        <v>1</v>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C54" s="2">
-        <v>5</v>
-      </c>
-      <c r="D54" s="2">
-        <v>5</v>
-      </c>
-      <c r="E54" s="2">
-        <v>5</v>
-      </c>
-      <c r="F54" s="2">
-        <v>2</v>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|㳞</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-㳞</t>
-        </is>
-      </c>
-      <c r="I54" s="2"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="2"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2">
-        <v>1</v>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C55" s="2">
-        <v>5</v>
-      </c>
-      <c r="D55" s="2">
-        <v>5</v>
-      </c>
-      <c r="E55" s="2">
-        <v>6</v>
-      </c>
-      <c r="F55" s="2">
-        <v>2</v>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|無</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하</t>
-        </is>
-      </c>
-      <c r="J55" s="4"/>
-      <c r="K55" s="2"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2">
-        <v>1</v>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C56" s="2">
-        <v>5</v>
-      </c>
-      <c r="D56" s="2">
-        <v>5</v>
-      </c>
-      <c r="E56" s="2">
-        <v>7</v>
-      </c>
-      <c r="F56" s="2">
-        <v>3</v>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="J56" s="4"/>
-      <c r="K56" s="2"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2">
-        <v>1</v>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C57" s="2">
-        <v>5</v>
-      </c>
-      <c r="D57" s="2">
-        <v>5</v>
-      </c>
-      <c r="E57" s="2">
-        <v>8</v>
-      </c>
-      <c r="F57" s="2">
-        <v>3</v>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I57" s="2"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="2"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2">
-        <v>1</v>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C58" s="2">
-        <v>5</v>
-      </c>
-      <c r="D58" s="2">
-        <v>5</v>
-      </c>
-      <c r="E58" s="2">
-        <v>9</v>
-      </c>
-      <c r="F58" s="2">
-        <v>3</v>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南|無|姑</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無
-姑</t>
-        </is>
-      </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">에에</t>
@@ -2780,16 +2793,16 @@
         </is>
       </c>
       <c r="C59" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D59" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E59" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F59" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
@@ -2803,7 +2816,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이</t>
+          <t xml:space="preserve">요</t>
         </is>
       </c>
       <c r="J59" s="4"/>
@@ -2819,32 +2832,28 @@
         </is>
       </c>
       <c r="C60" s="2">
+        <v>6</v>
+      </c>
+      <c r="D60" s="2">
+        <v>6</v>
+      </c>
+      <c r="E60" s="2">
         <v>5</v>
       </c>
-      <c r="D60" s="2">
-        <v>5</v>
-      </c>
-      <c r="E60" s="2">
-        <v>11</v>
-      </c>
       <c r="F60" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I60" s="2"/>
       <c r="J60" s="4"/>
       <c r="K60" s="2"/>
     </row>
@@ -2858,25 +2867,26 @@
         </is>
       </c>
       <c r="C61" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D61" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E61" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F61" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I61" s="2"/>
@@ -2899,10 +2909,10 @@
         <v>6</v>
       </c>
       <c r="E62" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F62" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
@@ -2916,7 +2926,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">얼</t>
+          <t xml:space="preserve">에</t>
         </is>
       </c>
       <c r="J62" s="4"/>
@@ -2938,10 +2948,10 @@
         <v>6</v>
       </c>
       <c r="E63" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F63" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
@@ -2954,7 +2964,11 @@
 潢</t>
         </is>
       </c>
-      <c r="I63" s="2"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤에</t>
+        </is>
+      </c>
       <c r="J63" s="4"/>
       <c r="K63" s="2"/>
     </row>
@@ -2974,10 +2988,10 @@
         <v>6</v>
       </c>
       <c r="E64" s="2">
+        <v>9</v>
+      </c>
+      <c r="F64" s="2">
         <v>3</v>
-      </c>
-      <c r="F64" s="2">
-        <v>1</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -2992,7 +3006,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삼</t>
+          <t xml:space="preserve">에에</t>
         </is>
       </c>
       <c r="J64" s="4"/>
@@ -3014,22 +3028,26 @@
         <v>6</v>
       </c>
       <c r="E65" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F65" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I65" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
       <c r="J65" s="4"/>
       <c r="K65" s="2"/>
     </row>
@@ -3049,25 +3067,24 @@
         <v>6</v>
       </c>
       <c r="E66" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F66" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|·</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-·</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">마</t>
+          <t xml:space="preserve">야</t>
         </is>
       </c>
       <c r="J66" s="4"/>
@@ -3089,20 +3106,20 @@
         <v>6</v>
       </c>
       <c r="E67" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F67" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|·</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-·</t>
+△</t>
         </is>
       </c>
       <c r="I67" s="2"/>
@@ -3119,30 +3136,30 @@
         </is>
       </c>
       <c r="C68" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D68" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E68" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F68" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">등</t>
+          <t xml:space="preserve">얼</t>
         </is>
       </c>
       <c r="J68" s="4"/>
@@ -3158,26 +3175,25 @@
         </is>
       </c>
       <c r="C69" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D69" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E69" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F69" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|潢</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-潢</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I69" s="2"/>
@@ -3194,34 +3210,37 @@
         </is>
       </c>
       <c r="C70" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D70" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E70" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F70" s="2">
-        <v>3</v>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無|南</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-南</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">개</t>
-        </is>
-      </c>
-      <c r="J70" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">삼</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 삼/쌈?</t>
+        </is>
+      </c>
       <c r="K70" s="2"/>
     </row>
     <row r="71">
@@ -3234,30 +3253,30 @@
         </is>
       </c>
       <c r="C71" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D71" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E71" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F71" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">디</t>
+          <t xml:space="preserve">마</t>
         </is>
       </c>
       <c r="J71" s="4"/>
@@ -3273,30 +3292,30 @@
         </is>
       </c>
       <c r="C72" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D72" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E72" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F72" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">어</t>
+          <t xml:space="preserve">둥</t>
         </is>
       </c>
       <c r="J72" s="4"/>
@@ -3312,25 +3331,25 @@
         </is>
       </c>
       <c r="C73" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D73" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E73" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F73" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I73" s="2"/>
@@ -3353,24 +3372,24 @@
         <v>7</v>
       </c>
       <c r="E74" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F74" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">내</t>
+          <t xml:space="preserve">개</t>
         </is>
       </c>
       <c r="J74" s="4"/>
@@ -3392,22 +3411,26 @@
         <v>7</v>
       </c>
       <c r="E75" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F75" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I75" s="2"/>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디</t>
+        </is>
+      </c>
       <c r="J75" s="4"/>
       <c r="K75" s="2"/>
     </row>
@@ -3427,24 +3450,24 @@
         <v>7</v>
       </c>
       <c r="E76" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F76" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삼</t>
+          <t xml:space="preserve">어</t>
         </is>
       </c>
       <c r="J76" s="4"/>
@@ -3466,31 +3489,28 @@
         <v>7</v>
       </c>
       <c r="E77" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F77" s="2">
-        <v>2</v>
-      </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사</t>
-        </is>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">빈 칸, 가사만 적힘</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|無</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+無</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라</t>
+        </is>
+      </c>
+      <c r="J77" s="4"/>
       <c r="K77" s="2"/>
     </row>
     <row r="78">
@@ -3503,28 +3523,32 @@
         </is>
       </c>
       <c r="C78" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D78" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E78" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F78" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I78" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">내</t>
+        </is>
+      </c>
       <c r="J78" s="4"/>
       <c r="K78" s="2"/>
     </row>
@@ -3538,34 +3562,33 @@
         </is>
       </c>
       <c r="C79" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D79" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E79" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F79" s="2">
-        <v>2</v>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|·</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-·</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">마</t>
-        </is>
-      </c>
-      <c r="J79" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I79" s="3"/>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비스듬한 짧은 획(–/·?)</t>
+        </is>
+      </c>
       <c r="K79" s="2"/>
     </row>
     <row r="80">
@@ -3578,32 +3601,28 @@
         </is>
       </c>
       <c r="C80" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D80" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E80" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F80" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">강</t>
-        </is>
-      </c>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I80" s="2"/>
       <c r="J80" s="4"/>
       <c r="K80" s="2"/>
     </row>
@@ -3617,33 +3636,37 @@
         </is>
       </c>
       <c r="C81" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D81" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E81" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F81" s="2">
-        <v>3</v>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="J81" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢 왼쪽 아래 작은 점 생략</t>
+        </is>
+      </c>
       <c r="K81" s="2"/>
     </row>
     <row r="82">
@@ -3656,30 +3679,30 @@
         </is>
       </c>
       <c r="C82" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D82" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E82" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F82" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">앙</t>
+          <t xml:space="preserve">아</t>
         </is>
       </c>
       <c r="J82" s="4"/>
@@ -3695,37 +3718,33 @@
         </is>
       </c>
       <c r="C83" s="2">
+        <v>8</v>
+      </c>
+      <c r="D83" s="2">
+        <v>8</v>
+      </c>
+      <c r="E83" s="2">
         <v>7</v>
       </c>
-      <c r="D83" s="2">
-        <v>7</v>
-      </c>
-      <c r="E83" s="2">
-        <v>10</v>
-      </c>
       <c r="F83" s="2">
-        <v>4</v>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아아</t>
-        </is>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞(氵仲)</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랑</t>
+        </is>
+      </c>
+      <c r="J83" s="4"/>
       <c r="K83" s="2"/>
     </row>
     <row r="84">
@@ -3738,25 +3757,25 @@
         </is>
       </c>
       <c r="C84" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D84" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E84" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F84" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -3777,29 +3796,33 @@
         </is>
       </c>
       <c r="C85" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D85" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E85" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F85" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|無</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-無</t>
-        </is>
-      </c>
-      <c r="I85" s="2"/>
+南</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앙</t>
+        </is>
+      </c>
       <c r="J85" s="4"/>
       <c r="K85" s="2"/>
     </row>
@@ -3819,24 +3842,25 @@
         <v>8</v>
       </c>
       <c r="E86" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F86" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">내</t>
+          <t xml:space="preserve">아아</t>
         </is>
       </c>
       <c r="J86" s="4"/>
@@ -3858,22 +3882,26 @@
         <v>8</v>
       </c>
       <c r="E87" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F87" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I87" s="2"/>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
       <c r="J87" s="4"/>
       <c r="K87" s="2"/>
     </row>
@@ -3893,339 +3921,28 @@
         <v>8</v>
       </c>
       <c r="E88" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F88" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I88" s="2"/>
       <c r="J88" s="4"/>
       <c r="K88" s="2"/>
     </row>
-    <row r="89">
-      <c r="A89" s="2">
-        <v>1</v>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C89" s="2">
-        <v>8</v>
-      </c>
-      <c r="D89" s="2">
-        <v>8</v>
-      </c>
-      <c r="E89" s="2">
-        <v>4</v>
-      </c>
-      <c r="F89" s="2">
-        <v>2</v>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|·</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-·</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사</t>
-        </is>
-      </c>
-      <c r="J89" s="4"/>
-      <c r="K89" s="2"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2">
-        <v>1</v>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C90" s="2">
-        <v>8</v>
-      </c>
-      <c r="D90" s="2">
-        <v>8</v>
-      </c>
-      <c r="E90" s="2">
-        <v>6</v>
-      </c>
-      <c r="F90" s="2">
-        <v>2</v>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="J90" s="4"/>
-      <c r="K90" s="2"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2">
-        <v>1</v>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C91" s="2">
-        <v>8</v>
-      </c>
-      <c r="D91" s="2">
-        <v>8</v>
-      </c>
-      <c r="E91" s="2">
-        <v>7</v>
-      </c>
-      <c r="F91" s="2">
-        <v>3</v>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">강</t>
-        </is>
-      </c>
-      <c r="J91" s="4"/>
-      <c r="K91" s="2"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2">
-        <v>1</v>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C92" s="2">
-        <v>8</v>
-      </c>
-      <c r="D92" s="2">
-        <v>8</v>
-      </c>
-      <c r="E92" s="2">
-        <v>8</v>
-      </c>
-      <c r="F92" s="2">
-        <v>3</v>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="J92" s="4"/>
-      <c r="K92" s="2"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2">
-        <v>1</v>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C93" s="2">
-        <v>8</v>
-      </c>
-      <c r="D93" s="2">
-        <v>8</v>
-      </c>
-      <c r="E93" s="2">
-        <v>9</v>
-      </c>
-      <c r="F93" s="2">
-        <v>3</v>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|南</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-南</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앙</t>
-        </is>
-      </c>
-      <c r="J93" s="4"/>
-      <c r="K93" s="2"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2">
-        <v>1</v>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C94" s="2">
-        <v>8</v>
-      </c>
-      <c r="D94" s="2">
-        <v>8</v>
-      </c>
-      <c r="E94" s="2">
-        <v>10</v>
-      </c>
-      <c r="F94" s="2">
-        <v>4</v>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無|南</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-南</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아아</t>
-        </is>
-      </c>
-      <c r="J94" s="4"/>
-      <c r="K94" s="2"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2">
-        <v>1</v>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C95" s="2">
-        <v>8</v>
-      </c>
-      <c r="D95" s="2">
-        <v>8</v>
-      </c>
-      <c r="E95" s="2">
-        <v>11</v>
-      </c>
-      <c r="F95" s="2">
-        <v>4</v>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="J95" s="4"/>
-      <c r="K95" s="2"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2">
-        <v>1</v>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/한강수 타령.png</t>
-        </is>
-      </c>
-      <c r="C96" s="2">
-        <v>8</v>
-      </c>
-      <c r="D96" s="2">
-        <v>8</v>
-      </c>
-      <c r="E96" s="2">
-        <v>12</v>
-      </c>
-      <c r="F96" s="2">
-        <v>4</v>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|·</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-·</t>
-        </is>
-      </c>
-      <c r="I96" s="2"/>
-      <c r="J96" s="4"/>
-      <c r="K96" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K96"/>
+  <autoFilter ref="A1:K88"/>
 </worksheet>
 </file>
 
@@ -4254,7 +3971,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="82.06" customHeight="1">
+    <row r="2" ht="77.61" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4277,14 +3994,14 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="82.06" customHeight="1">
+    <row r="3" ht="77.61" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
@@ -4294,9 +4011,9 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">내</t>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">얼</t>
         </is>
       </c>
       <c r="F3" s="21" t="inlineStr">
@@ -4304,9 +4021,9 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">얼</t>
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
         </is>
       </c>
       <c r="H3" s="21" t="inlineStr">
@@ -4314,39 +4031,39 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I3" s="27" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J3" s="21" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수</t>
+        </is>
+      </c>
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K3" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="L3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M3" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="N3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O3" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">수</t>
+      <c r="O3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">깊</t>
         </is>
       </c>
       <c r="P3" s="21" t="inlineStr">
@@ -4354,92 +4071,82 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q3" s="27" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">한</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="82.06" customHeight="1">
+    <row r="4" ht="77.61" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C4" s="28"/>
+      <c r="C4" s="24"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="28"/>
+      <c r="E4" s="25"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-–</t>
-        </is>
-      </c>
-      <c r="I4" s="28" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
+      <c r="H4" s="21"/>
+      <c r="I4" s="25"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K4" s="28" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
       </c>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-–</t>
-        </is>
-      </c>
-      <c r="M4" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">루</t>
-        </is>
-      </c>
+      <c r="L4" s="21"/>
+      <c r="M4" s="25"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O4" s="28"/>
+      <c r="O4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
       <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q4" s="28"/>
-    </row>
-    <row r="5" ht="82.06" customHeight="1">
+      <c r="Q4" s="25"/>
+    </row>
+    <row r="5" ht="77.61" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="C5" s="26"/>
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
@@ -4450,29 +4157,29 @@
 南</t>
         </is>
       </c>
-      <c r="G5" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">삼</t>
-        </is>
-      </c>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I5" s="29" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">에
 에</t>
         </is>
       </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하</t>
+        </is>
+      </c>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="K5" s="29" t="inlineStr">
+      <c r="K5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -4482,9 +4189,9 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M5" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">화</t>
+      <c r="M5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
         </is>
       </c>
       <c r="N5" s="21" t="inlineStr">
@@ -4493,9 +4200,9 @@
 無</t>
         </is>
       </c>
-      <c r="O5" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">삼</t>
+      <c r="O5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오</t>
         </is>
       </c>
       <c r="P5" s="21" t="inlineStr">
@@ -4503,221 +4210,190 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q5" s="29"/>
-    </row>
-    <row r="6" ht="82.06" customHeight="1">
+      <c r="Q5" s="26"/>
+    </row>
+    <row r="6" ht="77.61" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-–</t>
-        </is>
-      </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E6" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사</t>
-        </is>
-      </c>
+      <c r="D6" s="21"/>
+      <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G6" s="27"/>
-      <c r="H6" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I6" s="30" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J6" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="K6" s="30" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">뱃</t>
         </is>
       </c>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-–</t>
-        </is>
-      </c>
-      <c r="M6" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">뱃</t>
-        </is>
-      </c>
-      <c r="N6" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="O6" s="30"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="O6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">깊</t>
+        </is>
+      </c>
       <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q6" s="27" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="82.06" customHeight="1">
+    <row r="7" ht="77.61" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
-      <c r="C7" s="28"/>
+      <c r="C7" s="25"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E7" s="28"/>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마</t>
+        </is>
+      </c>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-–</t>
-        </is>
-      </c>
-      <c r="G7" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">마</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G7" s="25"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-㳞</t>
-        </is>
-      </c>
-      <c r="I7" s="28"/>
-      <c r="J7" s="21" t="inlineStr">
+㴌</t>
+        </is>
+      </c>
+      <c r="K7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">놀</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선</t>
+        </is>
+      </c>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-㳞</t>
-        </is>
-      </c>
-      <c r="K7" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">놀</t>
-        </is>
-      </c>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M7" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">놀</t>
-        </is>
-      </c>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-㳞</t>
-        </is>
-      </c>
-      <c r="O7" s="28"/>
-      <c r="P7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-–</t>
-        </is>
-      </c>
-      <c r="Q7" s="28"/>
-    </row>
-    <row r="8" ht="82.06" customHeight="1">
+㴌</t>
+        </is>
+      </c>
+      <c r="O7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">은</t>
+        </is>
+      </c>
+      <c r="P7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="Q7" s="24"/>
+    </row>
+    <row r="8" ht="77.61" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="21"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
-        </is>
-      </c>
-      <c r="E8" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">마</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-–</t>
-        </is>
-      </c>
-      <c r="G8" s="29"/>
+△</t>
+        </is>
+      </c>
+      <c r="G8" s="26"/>
       <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I8" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="inlineStr">
+      <c r="K8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="L8" s="21"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K8" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-–</t>
-        </is>
-      </c>
-      <c r="M8" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="O8" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">선</t>
+      <c r="O8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">으
+은</t>
         </is>
       </c>
       <c r="P8" s="21" t="inlineStr">
@@ -4725,18 +4401,18 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q8" s="29"/>
-    </row>
-    <row r="9" ht="82.06" customHeight="1">
+      <c r="Q8" s="26"/>
+    </row>
+    <row r="9" ht="77.61" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">강</t>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랑</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -4744,9 +4420,9 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E9" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">강</t>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">둥</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -4754,9 +4430,9 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G9" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">등</t>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -4764,7 +4440,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I9" s="27" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4774,19 +4450,19 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K9" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="L9" s="21" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M9" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가</t>
+      <c r="M9" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
@@ -4794,9 +4470,9 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O9" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">라</t>
+      <c r="O9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물</t>
         </is>
       </c>
       <c r="P9" s="21" t="inlineStr">
@@ -4804,20 +4480,20 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q9" s="27" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="82.06" customHeight="1">
+    <row r="10" ht="77.61" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4827,39 +4503,40 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E10" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
+      <c r="E10" s="25"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G10" s="28"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I10" s="28"/>
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤
+에</t>
+        </is>
+      </c>
+      <c r="H10" s="21"/>
+      <c r="I10" s="25"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K10" s="28"/>
+      <c r="K10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잔</t>
+        </is>
+      </c>
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="M10" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전</t>
+      <c r="M10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
         </is>
       </c>
       <c r="N10" s="21" t="inlineStr">
@@ -4867,9 +4544,9 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O10" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">고</t>
+      <c r="O10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">울</t>
         </is>
       </c>
       <c r="P10" s="21" t="inlineStr">
@@ -4878,13 +4555,13 @@
 潢</t>
         </is>
       </c>
-      <c r="Q10" s="28" t="inlineStr">
+      <c r="Q10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="82.06" customHeight="1">
+    <row r="11" ht="77.61" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4892,7 +4569,7 @@
 南</t>
         </is>
       </c>
-      <c r="C11" s="29" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">앙</t>
         </is>
@@ -4902,9 +4579,9 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E11" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앙</t>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -4913,22 +4590,22 @@
 南</t>
         </is>
       </c>
-      <c r="G11" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">개</t>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에
+에</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
-姑</t>
-        </is>
-      </c>
-      <c r="I11" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에
-에</t>
+南</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -4937,9 +4614,9 @@
 南</t>
         </is>
       </c>
-      <c r="K11" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
+      <c r="K11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">안</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -4948,9 +4625,9 @@
 南</t>
         </is>
       </c>
-      <c r="M11" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">안</t>
+      <c r="M11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오</t>
         </is>
       </c>
       <c r="N11" s="21" t="inlineStr">
@@ -4959,9 +4636,9 @@
 南</t>
         </is>
       </c>
-      <c r="O11" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">오</t>
+      <c r="O11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
         </is>
       </c>
       <c r="P11" s="21" t="inlineStr">
@@ -4970,13 +4647,13 @@
 南</t>
         </is>
       </c>
-      <c r="Q11" s="29" t="inlineStr">
+      <c r="Q11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="82.06" customHeight="1">
+    <row r="12" ht="77.61" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4984,21 +4661,20 @@
 南</t>
         </is>
       </c>
-      <c r="C12" s="27" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 아</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="E12" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아
-아</t>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -5006,9 +4682,9 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G12" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">디</t>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -5016,9 +4692,9 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I12" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -5026,9 +4702,9 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K12" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요</t>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -5036,9 +4712,9 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M12" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서</t>
         </is>
       </c>
       <c r="N12" s="21" t="inlineStr">
@@ -5046,9 +4722,9 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O12" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서</t>
+      <c r="O12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
         </is>
       </c>
       <c r="P12" s="21" t="inlineStr">
@@ -5056,20 +4732,20 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q12" s="27" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="82.06" customHeight="1">
+    <row r="13" ht="77.61" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5079,116 +4755,126 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E13" s="28" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M13" s="25"/>
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G13" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I13" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K13" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">오</t>
-        </is>
-      </c>
-      <c r="L13" s="21" t="inlineStr">
+      <c r="O13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤</t>
+        </is>
+      </c>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M13" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O13" s="28"/>
-      <c r="P13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q13" s="28"/>
-    </row>
-    <row r="14" ht="82.06" customHeight="1">
+      <c r="Q13" s="25"/>
+    </row>
+    <row r="14" ht="77.61" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
-        </is>
-      </c>
-      <c r="C14" s="29"/>
+△</t>
+        </is>
+      </c>
+      <c r="C14" s="26"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="E14" s="29"/>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라</t>
+        </is>
+      </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G14" s="29"/>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="G14" s="26"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I14" s="29"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K14" s="29"/>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I14" s="26"/>
+      <c r="J14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="K14" s="27"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M14" s="29"/>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="M14" s="26"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="O14" s="29"/>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="O14" s="26"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q14" s="29"/>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="Q14" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/한강수 타령.xlsx
+++ b/sheets/민요/검수/한강수 타령.xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/한강수 타령.xlsx
+++ b/sheets/민요/검수/한강수 타령.xlsx
@@ -3945,6 +3945,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -3965,10 +3968,10 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="77.61" customHeight="1">
+    <row r="2" ht="68.97" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3991,7 +3994,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="77.61" customHeight="1">
+    <row r="3" ht="102.71" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4074,7 +4077,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="77.61" customHeight="1">
+    <row r="4" ht="102.71" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -4130,7 +4133,7 @@
       </c>
       <c r="Q4" s="25"/>
     </row>
-    <row r="5" ht="77.61" customHeight="1">
+    <row r="5" ht="102.71" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4209,7 +4212,7 @@
       </c>
       <c r="Q5" s="26"/>
     </row>
-    <row r="6" ht="77.61" customHeight="1">
+    <row r="6" ht="102.71" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -4276,7 +4279,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="77.61" customHeight="1">
+    <row r="7" ht="102.71" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="25"/>
@@ -4337,7 +4340,7 @@
       </c>
       <c r="Q7" s="24"/>
     </row>
-    <row r="8" ht="77.61" customHeight="1">
+    <row r="8" ht="102.71" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4400,7 +4403,7 @@
       </c>
       <c r="Q8" s="26"/>
     </row>
-    <row r="9" ht="77.61" customHeight="1">
+    <row r="9" ht="102.71" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4483,7 +4486,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="77.61" customHeight="1">
+    <row r="10" ht="102.71" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4558,7 +4561,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="77.61" customHeight="1">
+    <row r="11" ht="102.71" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4650,7 +4653,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="77.61" customHeight="1">
+    <row r="12" ht="102.71" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4735,7 +4738,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="77.61" customHeight="1">
+    <row r="13" ht="102.71" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4810,7 +4813,7 @@
       </c>
       <c r="Q13" s="25"/>
     </row>
-    <row r="14" ht="77.61" customHeight="1">
+    <row r="14" ht="102.71" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4879,6 +4882,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="76"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/한강수 타령.xlsx
+++ b/sheets/민요/검수/한강수 타령.xlsx
@@ -3950,28 +3950,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="12" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="68.97" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="102.71" customHeight="true">
+    <row r="3" ht="96.05" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="102.71" customHeight="true">
+    <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="Q4" s="25"/>
     </row>
-    <row r="5" ht="102.71" customHeight="true">
+    <row r="5" ht="96.05" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="Q5" s="26"/>
     </row>
-    <row r="6" ht="102.71" customHeight="true">
+    <row r="6" ht="96.05" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="102.71" customHeight="true">
+    <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="25"/>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="Q7" s="24"/>
     </row>
-    <row r="8" ht="102.71" customHeight="true">
+    <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="Q8" s="26"/>
     </row>
-    <row r="9" ht="102.71" customHeight="true">
+    <row r="9" ht="96.05" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="102.71" customHeight="true">
+    <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="102.71" customHeight="true">
+    <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="102.71" customHeight="true">
+    <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="102.71" customHeight="true">
+    <row r="13" ht="96.05" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="Q13" s="25"/>
     </row>
-    <row r="14" ht="102.71" customHeight="true">
+    <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4882,6 +4882,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>